--- a/Codes_2025/Trial 3/Trial3_XGB_Followers_Results.xlsx
+++ b/Codes_2025/Trial 3/Trial3_XGB_Followers_Results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,10 +473,10 @@
         <v>5.93</v>
       </c>
       <c r="D2" t="n">
-        <v>5.843998432159424</v>
+        <v>5.944624900817871</v>
       </c>
       <c r="E2" t="n">
-        <v>0.08600156784057589</v>
+        <v>0.01462490081787138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -497,10 +497,10 @@
         <v>2.64</v>
       </c>
       <c r="D3" t="n">
-        <v>3.547864675521851</v>
+        <v>5.259338855743408</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9078646755218505</v>
+        <v>2.619338855743408</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -521,10 +521,10 @@
         <v>10.68</v>
       </c>
       <c r="D4" t="n">
-        <v>7.896418571472168</v>
+        <v>6.130778312683105</v>
       </c>
       <c r="E4" t="n">
-        <v>2.78358142852783</v>
+        <v>4.549221687316892</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -545,10 +545,10 @@
         <v>7.740000000000002</v>
       </c>
       <c r="D5" t="n">
-        <v>6.950012683868408</v>
+        <v>6.693601131439209</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7899873161315938</v>
+        <v>1.046398868560793</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -559,20 +559,20 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ireland</t>
         </is>
       </c>
       <c r="B6" t="n">
         <v>2025</v>
       </c>
       <c r="C6" t="n">
-        <v>37.81</v>
+        <v>19.89</v>
       </c>
       <c r="D6" t="n">
-        <v>14.04712390899658</v>
+        <v>5.944624900817871</v>
       </c>
       <c r="E6" t="n">
-        <v>23.76287609100342</v>
+        <v>13.94537509918213</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -583,20 +583,20 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>Latvia</t>
         </is>
       </c>
       <c r="B7" t="n">
         <v>2025</v>
       </c>
       <c r="C7" t="n">
-        <v>6.81</v>
+        <v>8.050000000000002</v>
       </c>
       <c r="D7" t="n">
-        <v>14.04712390899658</v>
+        <v>6.130778312683105</v>
       </c>
       <c r="E7" t="n">
-        <v>7.237123908996582</v>
+        <v>1.919221687316897</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -607,20 +607,20 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Lithuania</t>
         </is>
       </c>
       <c r="B8" t="n">
         <v>2025</v>
       </c>
       <c r="C8" t="n">
-        <v>19.89</v>
+        <v>7.989999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>5.535460472106934</v>
+        <v>6.693601131439209</v>
       </c>
       <c r="E8" t="n">
-        <v>14.35453952789306</v>
+        <v>1.29639886856079</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -631,20 +631,20 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Latvia</t>
+          <t>Luxembourg</t>
         </is>
       </c>
       <c r="B9" t="n">
         <v>2025</v>
       </c>
       <c r="C9" t="n">
-        <v>8.050000000000002</v>
+        <v>28.09</v>
       </c>
       <c r="D9" t="n">
-        <v>7.148344993591309</v>
+        <v>6.693601131439209</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9016550064086939</v>
+        <v>21.39639886856079</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -655,20 +655,20 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Lithuania</t>
+          <t>Malta</t>
         </is>
       </c>
       <c r="B10" t="n">
         <v>2025</v>
       </c>
       <c r="C10" t="n">
-        <v>7.989999999999999</v>
+        <v>33.88</v>
       </c>
       <c r="D10" t="n">
-        <v>8.258951187133789</v>
+        <v>7.127575397491455</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2689511871337897</v>
+        <v>26.75242460250855</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -679,20 +679,20 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Luxembourg</t>
+          <t>Slovakia</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>2025</v>
       </c>
       <c r="C11" t="n">
-        <v>28.09</v>
+        <v>5.56</v>
       </c>
       <c r="D11" t="n">
-        <v>6.287462711334229</v>
+        <v>5.944624900817871</v>
       </c>
       <c r="E11" t="n">
-        <v>21.80253728866577</v>
+        <v>0.3846249008178715</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -703,94 +703,22 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>Slovenia</t>
         </is>
       </c>
       <c r="B12" t="n">
         <v>2025</v>
       </c>
       <c r="C12" t="n">
-        <v>33.88</v>
+        <v>11.6</v>
       </c>
       <c r="D12" t="n">
-        <v>10.10160446166992</v>
+        <v>6.693601131439209</v>
       </c>
       <c r="E12" t="n">
-        <v>23.77839553833008</v>
+        <v>4.906398868560792</v>
       </c>
       <c r="F12" t="inlineStr">
-        <is>
-          <t>Followers</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C13" t="n">
-        <v>24.26000000000001</v>
-      </c>
-      <c r="D13" t="n">
-        <v>14.04712390899658</v>
-      </c>
-      <c r="E13" t="n">
-        <v>10.21287609100342</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Followers</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Slovakia</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C14" t="n">
-        <v>5.56</v>
-      </c>
-      <c r="D14" t="n">
-        <v>4.645389556884766</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.914610443115234</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Followers</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Slovenia</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>2025</v>
-      </c>
-      <c r="C15" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="D15" t="n">
-        <v>6.287462711334229</v>
-      </c>
-      <c r="E15" t="n">
-        <v>5.312537288665773</v>
-      </c>
-      <c r="F15" t="inlineStr">
         <is>
           <t>Followers</t>
         </is>
